--- a/Excel case study - 1.xlsx
+++ b/Excel case study - 1.xlsx
@@ -8,10 +8,10 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Manish k jha\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{EADF41BF-745D-4B50-ACBE-2FB3571946C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B513B5B-0020-40F8-A572-D6BA011482D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <workbookProtection lockStructure="1"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="758" activeTab="3" xr2:uid="{79EB00AA-E363-4462-86A0-44CFA398920C}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="758" activeTab="4" xr2:uid="{79EB00AA-E363-4462-86A0-44CFA398920C}"/>
   </bookViews>
   <sheets>
     <sheet name="Question 1" sheetId="2" r:id="rId1"/>
@@ -23,11 +23,28 @@
     <sheet name="SPORT" sheetId="5" r:id="rId7"/>
     <sheet name="LOCATION" sheetId="4" r:id="rId8"/>
   </sheets>
+  <definedNames>
+    <definedName name="Slicer_BLOODTYPE">#N/A</definedName>
+    <definedName name="Slicer_LANGUAGE">#N/A</definedName>
+    <definedName name="Slicer_SPORTS">#N/A</definedName>
+    <definedName name="Slicer_Years__BIRTHDATE">#N/A</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="0" r:id="rId9"/>
+    <pivotCache cacheId="1" r:id="rId9"/>
   </pivotCaches>
   <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{BBE1A952-AA13-448e-AADC-164F8A28A991}">
+      <x14:slicerCaches>
+        <x14:slicerCache r:id="rId10"/>
+        <x14:slicerCache r:id="rId11"/>
+        <x14:slicerCache r:id="rId12"/>
+        <x14:slicerCache r:id="rId13"/>
+      </x14:slicerCaches>
+    </ext>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{79F54976-1DA5-4618-B147-4CDE4B953A38}">
+      <x14:workbookPr/>
+    </ext>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
@@ -1417,7 +1434,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
   <numFmts count="4">
     <numFmt numFmtId="164" formatCode="000"/>
     <numFmt numFmtId="165" formatCode="dd/mmm/yyyy"/>
@@ -2126,10 +2143,15 @@
       </border>
     </dxf>
   </dxfs>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="2" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
+    <tableStyle name="PivotTable Style 1" table="0" count="0" xr9:uid="{18523CC2-228E-4457-94AB-401ADEEFBAAB}"/>
+    <tableStyle name="Slicer Style 1" pivot="0" table="0" count="0" xr9:uid="{F88D9253-BFE0-490D-951E-1E400CC09111}"/>
+  </tableStyles>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1">
+        <x14:slicerStyle name="Slicer Style 1"/>
+      </x14:slicerStyles>
     </ext>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
       <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
@@ -2138,8 +2160,321 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>12700</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>165101</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>12700</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>1</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+        <xdr:graphicFrame macro="">
+          <xdr:nvGraphicFramePr>
+            <xdr:cNvPr id="2" name="BLOODTYPE">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{603E27D5-A1C6-4316-B4D8-AAE50AC9DBA1}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvGraphicFramePr/>
+          </xdr:nvGraphicFramePr>
+          <xdr:xfrm>
+            <a:off x="0" y="0"/>
+            <a:ext cx="0" cy="0"/>
+          </xdr:xfrm>
+          <a:graphic>
+            <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2010/slicer">
+              <sle:slicer xmlns:sle="http://schemas.microsoft.com/office/drawing/2010/slicer" name="BLOODTYPE"/>
+            </a:graphicData>
+          </a:graphic>
+        </xdr:graphicFrame>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="0" name=""/>
+            <xdr:cNvSpPr>
+              <a:spLocks noTextEdit="1"/>
+            </xdr:cNvSpPr>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="9347200" y="349251"/>
+              <a:ext cx="1828800" cy="2044700"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:prstClr val="white"/>
+            </a:solidFill>
+            <a:ln w="1">
+              <a:solidFill>
+                <a:prstClr val="green"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:r>
+                <a:rPr lang="en-IN" sz="1100"/>
+                <a:t>This shape represents a slicer. Slicers are supported in Excel 2010 or later.
+If the shape was modified in an earlier version of Excel, or if the workbook was saved in Excel 2003 or earlier, the slicer cannot be used.</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>12700</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>133350</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>12700</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>79375</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+        <xdr:graphicFrame macro="">
+          <xdr:nvGraphicFramePr>
+            <xdr:cNvPr id="3" name="SPORTS">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{002ABE2B-239D-5692-6655-FFB35303F8A8}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvGraphicFramePr/>
+          </xdr:nvGraphicFramePr>
+          <xdr:xfrm>
+            <a:off x="0" y="0"/>
+            <a:ext cx="0" cy="0"/>
+          </xdr:xfrm>
+          <a:graphic>
+            <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2010/slicer">
+              <sle:slicer xmlns:sle="http://schemas.microsoft.com/office/drawing/2010/slicer" name="SPORTS"/>
+            </a:graphicData>
+          </a:graphic>
+        </xdr:graphicFrame>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="0" name=""/>
+            <xdr:cNvSpPr>
+              <a:spLocks noTextEdit="1"/>
+            </xdr:cNvSpPr>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="9347200" y="4921250"/>
+              <a:ext cx="1828800" cy="2524125"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:prstClr val="white"/>
+            </a:solidFill>
+            <a:ln w="1">
+              <a:solidFill>
+                <a:prstClr val="green"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:r>
+                <a:rPr lang="en-IN" sz="1100"/>
+                <a:t>This shape represents a slicer. Slicers are supported in Excel 2010 or later.
+If the shape was modified in an earlier version of Excel, or if the workbook was saved in Excel 2003 or earlier, the slicer cannot be used.</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>12700</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>12700</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>130175</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+        <xdr:graphicFrame macro="">
+          <xdr:nvGraphicFramePr>
+            <xdr:cNvPr id="4" name="Years (BIRTHDATE)">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{750CAB91-0216-CD16-E501-D87F6278CF8E}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvGraphicFramePr/>
+          </xdr:nvGraphicFramePr>
+          <xdr:xfrm>
+            <a:off x="0" y="0"/>
+            <a:ext cx="0" cy="0"/>
+          </xdr:xfrm>
+          <a:graphic>
+            <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2010/slicer">
+              <sle:slicer xmlns:sle="http://schemas.microsoft.com/office/drawing/2010/slicer" name="Years (BIRTHDATE)"/>
+            </a:graphicData>
+          </a:graphic>
+        </xdr:graphicFrame>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="0" name=""/>
+            <xdr:cNvSpPr>
+              <a:spLocks noTextEdit="1"/>
+            </xdr:cNvSpPr>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="9347200" y="2393950"/>
+              <a:ext cx="1828800" cy="2524125"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:prstClr val="white"/>
+            </a:solidFill>
+            <a:ln w="1">
+              <a:solidFill>
+                <a:prstClr val="green"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:r>
+                <a:rPr lang="en-IN" sz="1100"/>
+                <a:t>This shape represents a slicer. Slicers are supported in Excel 2010 or later.
+If the shape was modified in an earlier version of Excel, or if the workbook was saved in Excel 2003 or earlier, the slicer cannot be used.</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>12700</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>82551</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>12700</xdr:colOff>
+      <xdr:row>53</xdr:row>
+      <xdr:rowOff>6351</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+        <xdr:graphicFrame macro="">
+          <xdr:nvGraphicFramePr>
+            <xdr:cNvPr id="6" name="LANGUAGE">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A9C29B19-C2D2-392E-82D0-76669ADDFFE7}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvGraphicFramePr/>
+          </xdr:nvGraphicFramePr>
+          <xdr:xfrm>
+            <a:off x="0" y="0"/>
+            <a:ext cx="0" cy="0"/>
+          </xdr:xfrm>
+          <a:graphic>
+            <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2010/slicer">
+              <sle:slicer xmlns:sle="http://schemas.microsoft.com/office/drawing/2010/slicer" name="LANGUAGE"/>
+            </a:graphicData>
+          </a:graphic>
+        </xdr:graphicFrame>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="0" name=""/>
+            <xdr:cNvSpPr>
+              <a:spLocks noTextEdit="1"/>
+            </xdr:cNvSpPr>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="9347200" y="7448551"/>
+              <a:ext cx="1828800" cy="2317750"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:prstClr val="white"/>
+            </a:solidFill>
+            <a:ln w="1">
+              <a:solidFill>
+                <a:prstClr val="green"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:r>
+                <a:rPr lang="en-IN" sz="1100"/>
+                <a:t>This shape represents a slicer. Slicers are supported in Excel 2010 or later.
+If the shape was modified in an earlier version of Excel, or if the workbook was saved in Excel 2003 or earlier, the slicer cannot be used.</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2422,7 +2757,14 @@
       <sharedItems/>
     </cacheField>
     <cacheField name="BLOODTYPE" numFmtId="0">
-      <sharedItems/>
+      <sharedItems count="6">
+        <s v="A−"/>
+        <s v="O−"/>
+        <s v="B−"/>
+        <s v="A+"/>
+        <s v="O+"/>
+        <s v="B+"/>
+      </sharedItems>
     </cacheField>
     <cacheField name="SPORT LOCATION" numFmtId="0">
       <sharedItems count="2">
@@ -2560,7 +2902,7 @@
   </cacheFields>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
-      <x14:pivotCacheDefinition/>
+      <x14:pivotCacheDefinition pivotCacheId="1258232219"/>
     </ext>
   </extLst>
 </pivotCacheDefinition>
@@ -2584,7 +2926,7 @@
     <x v="0"/>
     <n v="94"/>
     <s v="Green"/>
-    <s v="A−"/>
+    <x v="0"/>
     <x v="0"/>
     <x v="0"/>
     <n v="80727"/>
@@ -2605,7 +2947,7 @@
     <x v="1"/>
     <n v="84.2"/>
     <s v="Brown"/>
-    <s v="O−"/>
+    <x v="1"/>
     <x v="0"/>
     <x v="1"/>
     <n v="87471"/>
@@ -2626,7 +2968,7 @@
     <x v="2"/>
     <n v="52.9"/>
     <s v="Amber"/>
-    <s v="A−"/>
+    <x v="0"/>
     <x v="1"/>
     <x v="2"/>
     <n v="64724"/>
@@ -2647,7 +2989,7 @@
     <x v="3"/>
     <n v="48.9"/>
     <s v="Green"/>
-    <s v="O−"/>
+    <x v="1"/>
     <x v="1"/>
     <x v="3"/>
     <n v="110823"/>
@@ -2668,7 +3010,7 @@
     <x v="4"/>
     <n v="84.8"/>
     <s v="Blue"/>
-    <s v="B−"/>
+    <x v="2"/>
     <x v="0"/>
     <x v="4"/>
     <n v="56916"/>
@@ -2689,7 +3031,7 @@
     <x v="5"/>
     <n v="83.2"/>
     <s v="Blue"/>
-    <s v="O−"/>
+    <x v="1"/>
     <x v="0"/>
     <x v="5"/>
     <n v="51133"/>
@@ -2710,7 +3052,7 @@
     <x v="6"/>
     <n v="61.1"/>
     <s v="Blue"/>
-    <s v="B−"/>
+    <x v="2"/>
     <x v="1"/>
     <x v="6"/>
     <n v="65465"/>
@@ -2731,7 +3073,7 @@
     <x v="7"/>
     <n v="105.7"/>
     <s v="Amber"/>
-    <s v="A+"/>
+    <x v="3"/>
     <x v="0"/>
     <x v="7"/>
     <n v="109885"/>
@@ -2752,7 +3094,7 @@
     <x v="8"/>
     <n v="65.3"/>
     <s v="Blue"/>
-    <s v="A+"/>
+    <x v="3"/>
     <x v="0"/>
     <x v="8"/>
     <n v="60061"/>
@@ -2773,7 +3115,7 @@
     <x v="9"/>
     <n v="62.9"/>
     <s v="Amber"/>
-    <s v="O+"/>
+    <x v="4"/>
     <x v="1"/>
     <x v="6"/>
     <n v="32758"/>
@@ -2794,7 +3136,7 @@
     <x v="10"/>
     <n v="104.3"/>
     <s v="Brown"/>
-    <s v="O+"/>
+    <x v="4"/>
     <x v="1"/>
     <x v="9"/>
     <n v="99613"/>
@@ -2815,7 +3157,7 @@
     <x v="11"/>
     <n v="100.7"/>
     <s v="Brown"/>
-    <s v="O+"/>
+    <x v="4"/>
     <x v="1"/>
     <x v="10"/>
     <n v="56595"/>
@@ -2836,7 +3178,7 @@
     <x v="12"/>
     <n v="70.900000000000006"/>
     <s v="Green"/>
-    <s v="A−"/>
+    <x v="0"/>
     <x v="1"/>
     <x v="11"/>
     <n v="117408"/>
@@ -2857,7 +3199,7 @@
     <x v="13"/>
     <n v="68.3"/>
     <s v="Gray"/>
-    <s v="A+"/>
+    <x v="3"/>
     <x v="1"/>
     <x v="12"/>
     <n v="64862"/>
@@ -2878,7 +3220,7 @@
     <x v="14"/>
     <n v="105.3"/>
     <s v="Gray"/>
-    <s v="O+"/>
+    <x v="4"/>
     <x v="0"/>
     <x v="13"/>
     <n v="10241"/>
@@ -2899,7 +3241,7 @@
     <x v="15"/>
     <n v="48.6"/>
     <s v="Blue"/>
-    <s v="O+"/>
+    <x v="4"/>
     <x v="1"/>
     <x v="3"/>
     <n v="88762"/>
@@ -2920,7 +3262,7 @@
     <x v="16"/>
     <n v="105.9"/>
     <s v="Blue"/>
-    <s v="A−"/>
+    <x v="0"/>
     <x v="0"/>
     <x v="14"/>
     <n v="80757"/>
@@ -2941,7 +3283,7 @@
     <x v="17"/>
     <n v="71.099999999999994"/>
     <s v="Blue"/>
-    <s v="A−"/>
+    <x v="0"/>
     <x v="1"/>
     <x v="15"/>
     <n v="88794"/>
@@ -2962,7 +3304,7 @@
     <x v="18"/>
     <n v="70.3"/>
     <s v="Blue"/>
-    <s v="A+"/>
+    <x v="3"/>
     <x v="0"/>
     <x v="16"/>
     <n v="63526"/>
@@ -2983,7 +3325,7 @@
     <x v="19"/>
     <n v="54.7"/>
     <s v="Brown"/>
-    <s v="O−"/>
+    <x v="1"/>
     <x v="0"/>
     <x v="17"/>
     <n v="46352"/>
@@ -3004,7 +3346,7 @@
     <x v="20"/>
     <n v="100.9"/>
     <s v="Blue"/>
-    <s v="B−"/>
+    <x v="2"/>
     <x v="1"/>
     <x v="18"/>
     <n v="106808"/>
@@ -3025,7 +3367,7 @@
     <x v="21"/>
     <n v="84.3"/>
     <s v="Green"/>
-    <s v="A+"/>
+    <x v="3"/>
     <x v="1"/>
     <x v="19"/>
     <n v="96468"/>
@@ -3046,7 +3388,7 @@
     <x v="22"/>
     <n v="66.8"/>
     <s v="Blue"/>
-    <s v="O+"/>
+    <x v="4"/>
     <x v="1"/>
     <x v="20"/>
     <n v="16526"/>
@@ -3067,7 +3409,7 @@
     <x v="23"/>
     <n v="59.4"/>
     <s v="Amber"/>
-    <s v="B−"/>
+    <x v="2"/>
     <x v="1"/>
     <x v="21"/>
     <n v="21891"/>
@@ -3088,7 +3430,7 @@
     <x v="24"/>
     <n v="77.8"/>
     <s v="Amber"/>
-    <s v="A+"/>
+    <x v="3"/>
     <x v="1"/>
     <x v="6"/>
     <n v="62037"/>
@@ -3109,7 +3451,7 @@
     <x v="25"/>
     <n v="85.9"/>
     <s v="Blue"/>
-    <s v="B+"/>
+    <x v="5"/>
     <x v="0"/>
     <x v="0"/>
     <n v="89737"/>
@@ -3130,7 +3472,7 @@
     <x v="26"/>
     <n v="93.4"/>
     <s v="Amber"/>
-    <s v="B+"/>
+    <x v="5"/>
     <x v="0"/>
     <x v="22"/>
     <n v="41039"/>
@@ -3151,7 +3493,7 @@
     <x v="27"/>
     <n v="95.5"/>
     <s v="Gray"/>
-    <s v="O−"/>
+    <x v="1"/>
     <x v="1"/>
     <x v="11"/>
     <n v="28458"/>
@@ -3172,7 +3514,7 @@
     <x v="28"/>
     <n v="52.2"/>
     <s v="Blue"/>
-    <s v="O+"/>
+    <x v="4"/>
     <x v="1"/>
     <x v="6"/>
     <n v="55007"/>
@@ -3193,7 +3535,7 @@
     <x v="29"/>
     <n v="74.599999999999994"/>
     <s v="Blue"/>
-    <s v="B+"/>
+    <x v="5"/>
     <x v="1"/>
     <x v="23"/>
     <n v="69041"/>
@@ -3214,7 +3556,7 @@
     <x v="30"/>
     <n v="81.7"/>
     <s v="Amber"/>
-    <s v="O−"/>
+    <x v="1"/>
     <x v="0"/>
     <x v="22"/>
     <n v="86262"/>
@@ -3235,7 +3577,7 @@
     <x v="31"/>
     <n v="78.099999999999994"/>
     <s v="Blue"/>
-    <s v="O+"/>
+    <x v="4"/>
     <x v="1"/>
     <x v="20"/>
     <n v="19234"/>
@@ -3256,7 +3598,7 @@
     <x v="32"/>
     <n v="57.1"/>
     <s v="Green"/>
-    <s v="O+"/>
+    <x v="4"/>
     <x v="0"/>
     <x v="24"/>
     <n v="95123"/>
@@ -3277,7 +3619,7 @@
     <x v="33"/>
     <n v="56"/>
     <s v="Blue"/>
-    <s v="B+"/>
+    <x v="5"/>
     <x v="1"/>
     <x v="18"/>
     <n v="62761"/>
@@ -3298,7 +3640,7 @@
     <x v="34"/>
     <n v="88.6"/>
     <s v="Amber"/>
-    <s v="O+"/>
+    <x v="4"/>
     <x v="1"/>
     <x v="25"/>
     <n v="108431"/>
@@ -3319,7 +3661,7 @@
     <x v="35"/>
     <n v="78.2"/>
     <s v="Brown"/>
-    <s v="O−"/>
+    <x v="1"/>
     <x v="1"/>
     <x v="18"/>
     <n v="66268"/>
@@ -3340,7 +3682,7 @@
     <x v="36"/>
     <n v="95.8"/>
     <s v="Blue"/>
-    <s v="B−"/>
+    <x v="2"/>
     <x v="1"/>
     <x v="26"/>
     <n v="33970"/>
@@ -3361,7 +3703,7 @@
     <x v="37"/>
     <n v="59.7"/>
     <s v="Gray"/>
-    <s v="O−"/>
+    <x v="1"/>
     <x v="0"/>
     <x v="0"/>
     <n v="71352"/>
@@ -3382,7 +3724,7 @@
     <x v="38"/>
     <n v="77.7"/>
     <s v="Gray"/>
-    <s v="B−"/>
+    <x v="2"/>
     <x v="1"/>
     <x v="21"/>
     <n v="116376"/>
@@ -3403,7 +3745,7 @@
     <x v="39"/>
     <n v="98"/>
     <s v="Blue"/>
-    <s v="A−"/>
+    <x v="0"/>
     <x v="1"/>
     <x v="20"/>
     <n v="114144"/>
@@ -3424,7 +3766,7 @@
     <x v="40"/>
     <n v="51.9"/>
     <s v="Amber"/>
-    <s v="O−"/>
+    <x v="1"/>
     <x v="1"/>
     <x v="27"/>
     <n v="79872"/>
@@ -3445,7 +3787,7 @@
     <x v="41"/>
     <n v="55.6"/>
     <s v="Brown"/>
-    <s v="O+"/>
+    <x v="4"/>
     <x v="0"/>
     <x v="28"/>
     <n v="101969"/>
@@ -3466,7 +3808,7 @@
     <x v="42"/>
     <n v="102.3"/>
     <s v="Amber"/>
-    <s v="O+"/>
+    <x v="4"/>
     <x v="1"/>
     <x v="21"/>
     <n v="50659"/>
@@ -3487,7 +3829,7 @@
     <x v="43"/>
     <n v="58.8"/>
     <s v="Gray"/>
-    <s v="O−"/>
+    <x v="1"/>
     <x v="1"/>
     <x v="27"/>
     <n v="58215"/>
@@ -3508,7 +3850,7 @@
     <x v="44"/>
     <n v="63.8"/>
     <s v="Blue"/>
-    <s v="O+"/>
+    <x v="4"/>
     <x v="0"/>
     <x v="29"/>
     <n v="39935"/>
@@ -3529,7 +3871,7 @@
     <x v="45"/>
     <n v="98.6"/>
     <s v="Amber"/>
-    <s v="B+"/>
+    <x v="5"/>
     <x v="1"/>
     <x v="20"/>
     <n v="44865"/>
@@ -3550,7 +3892,7 @@
     <x v="46"/>
     <n v="61.8"/>
     <s v="Gray"/>
-    <s v="O−"/>
+    <x v="1"/>
     <x v="1"/>
     <x v="20"/>
     <n v="90478"/>
@@ -3571,7 +3913,7 @@
     <x v="47"/>
     <n v="50"/>
     <s v="Amber"/>
-    <s v="O+"/>
+    <x v="4"/>
     <x v="1"/>
     <x v="2"/>
     <n v="38965"/>
@@ -3592,7 +3934,7 @@
     <x v="48"/>
     <n v="45.9"/>
     <s v="Blue"/>
-    <s v="A−"/>
+    <x v="0"/>
     <x v="1"/>
     <x v="30"/>
     <n v="35387"/>
@@ -3613,7 +3955,7 @@
     <x v="49"/>
     <n v="92.5"/>
     <s v="Green"/>
-    <s v="A+"/>
+    <x v="3"/>
     <x v="0"/>
     <x v="31"/>
     <n v="20532"/>
@@ -3622,7 +3964,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{30A03E32-DC89-490C-8B19-A733C5A02714}" name="PivotTable1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" colHeaderCaption="">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{30A03E32-DC89-490C-8B19-A733C5A02714}" name="PivotTable1" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" colHeaderCaption="">
   <location ref="B4:D16" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="22">
     <pivotField dataField="1" numFmtId="164" showAll="0"/>
@@ -3901,7 +4243,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{644026A6-A2D0-4095-A994-1E6A858A9C96}" name="PivotTable1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" showDrill="0" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{644026A6-A2D0-4095-A994-1E6A858A9C96}" name="PivotTable1" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" showDrill="0" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
   <location ref="A3:H53" firstHeaderRow="1" firstDataRow="1" firstDataCol="8" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="22">
     <pivotField axis="axisRow" compact="0" numFmtId="164" outline="0" showAll="0" defaultSubtotal="0">
@@ -4160,7 +4502,16 @@
     </pivotField>
     <pivotField compact="0" numFmtId="166" outline="0" showAll="0" defaultSubtotal="0"/>
     <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
-    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0">
+      <items count="6">
+        <item x="0"/>
+        <item x="3"/>
+        <item x="2"/>
+        <item x="5"/>
+        <item x="1"/>
+        <item x="4"/>
+      </items>
+    </pivotField>
     <pivotField axis="axisPage" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0" defaultSubtotal="0">
       <items count="2">
         <item x="0"/>
@@ -4802,7 +5153,7 @@
   <pageFields count="1">
     <pageField fld="16" hier="-1"/>
   </pageFields>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <pivotTableStyleInfo name="PivotStyleDark7" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
       <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
@@ -4812,6 +5163,163 @@
     </ext>
   </extLst>
 </pivotTableDefinition>
+</file>
+
+<file path=xl/slicerCaches/slicerCache1.xml><?xml version="1.0" encoding="utf-8"?>
+<slicerCacheDefinition xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10" name="Slicer_BLOODTYPE" xr10:uid="{B141395B-FE15-4768-80C9-E7B41B978D60}" sourceName="BLOODTYPE">
+  <pivotTables>
+    <pivotTable tabId="11" name="PivotTable1"/>
+  </pivotTables>
+  <data>
+    <tabular pivotCacheId="1258232219">
+      <items count="6">
+        <i x="0" s="1"/>
+        <i x="3" s="1"/>
+        <i x="2" s="1"/>
+        <i x="5" s="1"/>
+        <i x="1" s="1"/>
+        <i x="4" s="1"/>
+      </items>
+    </tabular>
+  </data>
+</slicerCacheDefinition>
+</file>
+
+<file path=xl/slicerCaches/slicerCache2.xml><?xml version="1.0" encoding="utf-8"?>
+<slicerCacheDefinition xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10" name="Slicer_SPORTS" xr10:uid="{99886166-D3AC-4279-998E-0B07AA147436}" sourceName="SPORTS">
+  <pivotTables>
+    <pivotTable tabId="11" name="PivotTable1"/>
+  </pivotTables>
+  <data>
+    <tabular pivotCacheId="1258232219">
+      <items count="32">
+        <i x="3" s="1"/>
+        <i x="10" s="1"/>
+        <i x="27" s="1"/>
+        <i x="17" s="1"/>
+        <i x="20" s="1"/>
+        <i x="30" s="1"/>
+        <i x="1" s="1"/>
+        <i x="21" s="1"/>
+        <i x="12" s="1"/>
+        <i x="7" s="1"/>
+        <i x="13" s="1"/>
+        <i x="15" s="1"/>
+        <i x="6" s="1"/>
+        <i x="0" s="1"/>
+        <i x="24" s="1"/>
+        <i x="19" s="1"/>
+        <i x="5" s="1"/>
+        <i x="2" s="1"/>
+        <i x="9" s="1"/>
+        <i x="23" s="1"/>
+        <i x="28" s="1"/>
+        <i x="14" s="1"/>
+        <i x="25" s="1"/>
+        <i x="29" s="1"/>
+        <i x="11" s="1"/>
+        <i x="26" s="1"/>
+        <i x="8" s="1"/>
+        <i x="16" s="1"/>
+        <i x="31" s="1"/>
+        <i x="18" s="1"/>
+        <i x="22" s="1"/>
+        <i x="4" s="1"/>
+      </items>
+    </tabular>
+  </data>
+</slicerCacheDefinition>
+</file>
+
+<file path=xl/slicerCaches/slicerCache3.xml><?xml version="1.0" encoding="utf-8"?>
+<slicerCacheDefinition xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10" name="Slicer_Years__BIRTHDATE" xr10:uid="{76023472-9F69-41C7-9C08-97D9174E22A9}" sourceName="Years (BIRTHDATE)">
+  <pivotTables>
+    <pivotTable tabId="11" name="PivotTable1"/>
+  </pivotTables>
+  <data>
+    <tabular pivotCacheId="1258232219">
+      <items count="47">
+        <i x="1" s="1"/>
+        <i x="5" s="1"/>
+        <i x="6" s="1"/>
+        <i x="9" s="1"/>
+        <i x="10" s="1"/>
+        <i x="11" s="1"/>
+        <i x="12" s="1"/>
+        <i x="14" s="1"/>
+        <i x="15" s="1"/>
+        <i x="16" s="1"/>
+        <i x="17" s="1"/>
+        <i x="18" s="1"/>
+        <i x="19" s="1"/>
+        <i x="20" s="1"/>
+        <i x="21" s="1"/>
+        <i x="22" s="1"/>
+        <i x="23" s="1"/>
+        <i x="24" s="1"/>
+        <i x="25" s="1"/>
+        <i x="26" s="1"/>
+        <i x="27" s="1"/>
+        <i x="28" s="1"/>
+        <i x="29" s="1"/>
+        <i x="30" s="1"/>
+        <i x="32" s="1"/>
+        <i x="33" s="1"/>
+        <i x="34" s="1"/>
+        <i x="35" s="1"/>
+        <i x="36" s="1"/>
+        <i x="38" s="1"/>
+        <i x="39" s="1"/>
+        <i x="40" s="1"/>
+        <i x="42" s="1"/>
+        <i x="43" s="1"/>
+        <i x="45" s="1"/>
+        <i x="0" s="1" nd="1"/>
+        <i x="46" s="1" nd="1"/>
+        <i x="2" s="1" nd="1"/>
+        <i x="3" s="1" nd="1"/>
+        <i x="4" s="1" nd="1"/>
+        <i x="7" s="1" nd="1"/>
+        <i x="8" s="1" nd="1"/>
+        <i x="13" s="1" nd="1"/>
+        <i x="31" s="1" nd="1"/>
+        <i x="37" s="1" nd="1"/>
+        <i x="41" s="1" nd="1"/>
+        <i x="44" s="1" nd="1"/>
+      </items>
+    </tabular>
+  </data>
+</slicerCacheDefinition>
+</file>
+
+<file path=xl/slicerCaches/slicerCache4.xml><?xml version="1.0" encoding="utf-8"?>
+<slicerCacheDefinition xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10" name="Slicer_LANGUAGE" xr10:uid="{16031147-84DF-40A3-B75B-9CAA23B71FA2}" sourceName="LANGUAGE">
+  <pivotTables>
+    <pivotTable tabId="11" name="PivotTable1"/>
+  </pivotTables>
+  <data>
+    <tabular pivotCacheId="1258232219">
+      <items count="7">
+        <i x="5" s="1"/>
+        <i x="0" s="1"/>
+        <i x="3" s="1"/>
+        <i x="2" s="1"/>
+        <i x="1" s="1"/>
+        <i x="4" s="1"/>
+        <i x="6" s="1"/>
+      </items>
+    </tabular>
+  </data>
+</slicerCacheDefinition>
+</file>
+
+<file path=xl/slicers/slicer1.xml><?xml version="1.0" encoding="utf-8"?>
+<slicers xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10">
+  <slicer name="BLOODTYPE" xr10:uid="{11FB3828-0929-4C57-8C32-05127AC439D0}" cache="Slicer_BLOODTYPE" caption="BLOODTYPE" style="SlicerStyleLight6" rowHeight="241300"/>
+  <slicer name="SPORTS" xr10:uid="{6A6AC2ED-F264-4DE8-869B-69B1E479EC0B}" cache="Slicer_SPORTS" caption="SPORTS" startItem="11" style="SlicerStyleLight6" rowHeight="241300"/>
+  <slicer name="Years (BIRTHDATE)" xr10:uid="{D6B4D235-6EEE-43EE-BA1E-4B897B2C2CDE}" cache="Slicer_Years__BIRTHDATE" caption="Years (BIRTHDATE)" startItem="21" style="SlicerStyleLight6" rowHeight="241300"/>
+  <slicer name="LANGUAGE" xr10:uid="{00DA4E15-DD02-4547-A294-574A73F0824D}" cache="Slicer_LANGUAGE" caption="LANGUAGE" style="SlicerStyleLight6" rowHeight="241300"/>
+</slicers>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -5666,7 +6174,7 @@
   <sheetPr>
     <tabColor rgb="FFFF0000"/>
   </sheetPr>
-  <dimension ref="B2:J16"/>
+  <dimension ref="B4:J16"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="18.6328125" bestFit="1" customWidth="1"/>
@@ -5677,23 +6185,6 @@
     <col min="8" max="8" width="11.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:10" x14ac:dyDescent="0.35">
-      <c r="H2" s="55" t="s">
-        <v>286</v>
-      </c>
-      <c r="I2" s="55"/>
-    </row>
-    <row r="3" spans="2:10" x14ac:dyDescent="0.35">
-      <c r="G3" s="5" t="s">
-        <v>228</v>
-      </c>
-      <c r="H3" s="43" t="s">
-        <v>142</v>
-      </c>
-      <c r="I3" s="43" t="s">
-        <v>138</v>
-      </c>
-    </row>
     <row r="4" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B4" s="44" t="s">
         <v>284</v>
@@ -5702,17 +6193,10 @@
         <v>285</v>
       </c>
       <c r="D4" s="2"/>
-      <c r="G4" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="H4" s="2">
-        <f>COUNTIFS(SPORTSMEN!$K$1:$K$51,ANALYSIS!$G4,SPORTSMEN!$I$1:$I$51,ANALYSIS!$H$3)</f>
-        <v>2</v>
-      </c>
-      <c r="I4" s="2">
-        <f>COUNTIFS(SPORTSMEN!$K$1:$K$51,ANALYSIS!$G4,SPORTSMEN!$I$1:$I$51,$I$3)</f>
-        <v>1</v>
-      </c>
+      <c r="H4" s="55" t="s">
+        <v>286</v>
+      </c>
+      <c r="I4" s="55"/>
       <c r="J4" s="1"/>
     </row>
     <row r="5" spans="2:10" x14ac:dyDescent="0.35">
@@ -5725,16 +6209,14 @@
       <c r="D5" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="G5" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="H5" s="2">
-        <f>COUNTIFS(SPORTSMEN!$K$1:$K$51,ANALYSIS!$G5,SPORTSMEN!$I$1:$I$51,ANALYSIS!$H$3)</f>
-        <v>2</v>
-      </c>
-      <c r="I5" s="2">
-        <f>COUNTIFS(SPORTSMEN!$K$1:$K$51,ANALYSIS!$G5,SPORTSMEN!$I$1:$I$51,$I$3)</f>
-        <v>6</v>
+      <c r="G5" s="5" t="s">
+        <v>228</v>
+      </c>
+      <c r="H5" s="43" t="s">
+        <v>142</v>
+      </c>
+      <c r="I5" s="43" t="s">
+        <v>138</v>
       </c>
     </row>
     <row r="6" spans="2:10" x14ac:dyDescent="0.35">
@@ -5748,14 +6230,14 @@
         <v>2</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="H6" s="2">
-        <f>COUNTIFS(SPORTSMEN!$K$1:$K$51,ANALYSIS!$G6,SPORTSMEN!$I$1:$I$51,ANALYSIS!$H$3)</f>
+        <f>COUNTIFS(SPORTSMEN!$K$1:$K$51,ANALYSIS!$G6,SPORTSMEN!$I$1:$I$51,ANALYSIS!$H$5)</f>
         <v>2</v>
       </c>
       <c r="I6" s="2">
-        <f>COUNTIFS(SPORTSMEN!$K$1:$K$51,ANALYSIS!$G6,SPORTSMEN!$I$1:$I$51,$I$3)</f>
+        <f>COUNTIFS(SPORTSMEN!$K$1:$K$51,ANALYSIS!$G6,SPORTSMEN!$I$1:$I$51,$I$5)</f>
         <v>1</v>
       </c>
     </row>
@@ -5770,15 +6252,15 @@
         <v>2</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>144</v>
+        <v>151</v>
       </c>
       <c r="H7" s="2">
-        <f>COUNTIFS(SPORTSMEN!$K$1:$K$51,ANALYSIS!$G7,SPORTSMEN!$I$1:$I$51,ANALYSIS!$H$3)</f>
+        <f>COUNTIFS(SPORTSMEN!$K$1:$K$51,ANALYSIS!$G7,SPORTSMEN!$I$1:$I$51,ANALYSIS!$H$5)</f>
         <v>2</v>
       </c>
       <c r="I7" s="2">
-        <f>COUNTIFS(SPORTSMEN!$K$1:$K$51,ANALYSIS!$G7,SPORTSMEN!$I$1:$I$51,$I$3)</f>
-        <v>0</v>
+        <f>COUNTIFS(SPORTSMEN!$K$1:$K$51,ANALYSIS!$G7,SPORTSMEN!$I$1:$I$51,$I$5)</f>
+        <v>6</v>
       </c>
     </row>
     <row r="8" spans="2:10" x14ac:dyDescent="0.35">
@@ -5792,15 +6274,15 @@
         <v>2</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="H8" s="2">
-        <f>COUNTIFS(SPORTSMEN!$K$1:$K$51,ANALYSIS!$G8,SPORTSMEN!$I$1:$I$51,ANALYSIS!$H$3)</f>
-        <v>6</v>
+        <f>COUNTIFS(SPORTSMEN!$K$1:$K$51,ANALYSIS!$G8,SPORTSMEN!$I$1:$I$51,ANALYSIS!$H$5)</f>
+        <v>2</v>
       </c>
       <c r="I8" s="2">
-        <f>COUNTIFS(SPORTSMEN!$K$1:$K$51,ANALYSIS!$G8,SPORTSMEN!$I$1:$I$51,$I$3)</f>
-        <v>3</v>
+        <f>COUNTIFS(SPORTSMEN!$K$1:$K$51,ANALYSIS!$G8,SPORTSMEN!$I$1:$I$51,$I$5)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="2:10" x14ac:dyDescent="0.35">
@@ -5812,15 +6294,15 @@
         <v>2</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="H9" s="2">
-        <f>COUNTIFS(SPORTSMEN!$K$1:$K$51,ANALYSIS!$G9,SPORTSMEN!$I$1:$I$51,ANALYSIS!$H$3)</f>
-        <v>4</v>
+        <f>COUNTIFS(SPORTSMEN!$K$1:$K$51,ANALYSIS!$G9,SPORTSMEN!$I$1:$I$51,ANALYSIS!$H$5)</f>
+        <v>2</v>
       </c>
       <c r="I9" s="2">
-        <f>COUNTIFS(SPORTSMEN!$K$1:$K$51,ANALYSIS!$G9,SPORTSMEN!$I$1:$I$51,$I$3)</f>
-        <v>1</v>
+        <f>COUNTIFS(SPORTSMEN!$K$1:$K$51,ANALYSIS!$G9,SPORTSMEN!$I$1:$I$51,$I$5)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="2:10" x14ac:dyDescent="0.35">
@@ -5834,15 +6316,15 @@
         <v>6</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>164</v>
+        <v>156</v>
       </c>
       <c r="H10" s="2">
-        <f>COUNTIFS(SPORTSMEN!$K$1:$K$51,ANALYSIS!$G10,SPORTSMEN!$I$1:$I$51,ANALYSIS!$H$3)</f>
-        <v>1</v>
+        <f>COUNTIFS(SPORTSMEN!$K$1:$K$51,ANALYSIS!$G10,SPORTSMEN!$I$1:$I$51,ANALYSIS!$H$5)</f>
+        <v>6</v>
       </c>
       <c r="I10" s="2">
-        <f>COUNTIFS(SPORTSMEN!$K$1:$K$51,ANALYSIS!$G10,SPORTSMEN!$I$1:$I$51,$I$3)</f>
-        <v>2</v>
+        <f>COUNTIFS(SPORTSMEN!$K$1:$K$51,ANALYSIS!$G10,SPORTSMEN!$I$1:$I$51,$I$5)</f>
+        <v>3</v>
       </c>
     </row>
     <row r="11" spans="2:10" x14ac:dyDescent="0.35">
@@ -5856,15 +6338,15 @@
         <v>4</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>161</v>
+        <v>149</v>
       </c>
       <c r="H11" s="2">
-        <f>COUNTIFS(SPORTSMEN!$K$1:$K$51,ANALYSIS!$G11,SPORTSMEN!$I$1:$I$51,ANALYSIS!$H$3)</f>
-        <v>0</v>
+        <f>COUNTIFS(SPORTSMEN!$K$1:$K$51,ANALYSIS!$G11,SPORTSMEN!$I$1:$I$51,ANALYSIS!$H$5)</f>
+        <v>4</v>
       </c>
       <c r="I11" s="2">
-        <f>COUNTIFS(SPORTSMEN!$K$1:$K$51,ANALYSIS!$G11,SPORTSMEN!$I$1:$I$51,$I$3)</f>
-        <v>3</v>
+        <f>COUNTIFS(SPORTSMEN!$K$1:$K$51,ANALYSIS!$G11,SPORTSMEN!$I$1:$I$51,$I$5)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="2:10" x14ac:dyDescent="0.35">
@@ -5878,15 +6360,15 @@
         <v>1</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="H12" s="2">
-        <f>COUNTIFS(SPORTSMEN!$K$1:$K$51,ANALYSIS!$G12,SPORTSMEN!$I$1:$I$51,ANALYSIS!$H$3)</f>
+        <f>COUNTIFS(SPORTSMEN!$K$1:$K$51,ANALYSIS!$G12,SPORTSMEN!$I$1:$I$51,ANALYSIS!$H$5)</f>
         <v>1</v>
       </c>
       <c r="I12" s="2">
-        <f>COUNTIFS(SPORTSMEN!$K$1:$K$51,ANALYSIS!$G12,SPORTSMEN!$I$1:$I$51,$I$3)</f>
-        <v>1</v>
+        <f>COUNTIFS(SPORTSMEN!$K$1:$K$51,ANALYSIS!$G12,SPORTSMEN!$I$1:$I$51,$I$5)</f>
+        <v>2</v>
       </c>
     </row>
     <row r="13" spans="2:10" x14ac:dyDescent="0.35">
@@ -5898,14 +6380,14 @@
       </c>
       <c r="D13" s="2"/>
       <c r="G13" s="2" t="s">
-        <v>146</v>
+        <v>161</v>
       </c>
       <c r="H13" s="2">
-        <f>COUNTIFS(SPORTSMEN!$K$1:$K$51,ANALYSIS!$G13,SPORTSMEN!$I$1:$I$51,ANALYSIS!$H$3)</f>
-        <v>2</v>
+        <f>COUNTIFS(SPORTSMEN!$K$1:$K$51,ANALYSIS!$G13,SPORTSMEN!$I$1:$I$51,ANALYSIS!$H$5)</f>
+        <v>0</v>
       </c>
       <c r="I13" s="2">
-        <f>COUNTIFS(SPORTSMEN!$K$1:$K$51,ANALYSIS!$G13,SPORTSMEN!$I$1:$I$51,$I$3)</f>
+        <f>COUNTIFS(SPORTSMEN!$K$1:$K$51,ANALYSIS!$G13,SPORTSMEN!$I$1:$I$51,$I$5)</f>
         <v>3</v>
       </c>
     </row>
@@ -5920,15 +6402,15 @@
         <v>1</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>140</v>
+        <v>167</v>
       </c>
       <c r="H14" s="2">
-        <f>COUNTIFS(SPORTSMEN!$K$1:$K$51,ANALYSIS!$G14,SPORTSMEN!$I$1:$I$51,ANALYSIS!$H$3)</f>
-        <v>3</v>
+        <f>COUNTIFS(SPORTSMEN!$K$1:$K$51,ANALYSIS!$G14,SPORTSMEN!$I$1:$I$51,ANALYSIS!$H$5)</f>
+        <v>1</v>
       </c>
       <c r="I14" s="2">
-        <f>COUNTIFS(SPORTSMEN!$K$1:$K$51,ANALYSIS!$G14,SPORTSMEN!$I$1:$I$51,$I$3)</f>
-        <v>4</v>
+        <f>COUNTIFS(SPORTSMEN!$K$1:$K$51,ANALYSIS!$G14,SPORTSMEN!$I$1:$I$51,$I$5)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="15" spans="2:10" x14ac:dyDescent="0.35">
@@ -5941,6 +6423,17 @@
       <c r="D15" s="2">
         <v>2</v>
       </c>
+      <c r="G15" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="H15" s="2">
+        <f>COUNTIFS(SPORTSMEN!$K$1:$K$51,ANALYSIS!$G15,SPORTSMEN!$I$1:$I$51,ANALYSIS!$H$5)</f>
+        <v>2</v>
+      </c>
+      <c r="I15" s="2">
+        <f>COUNTIFS(SPORTSMEN!$K$1:$K$51,ANALYSIS!$G15,SPORTSMEN!$I$1:$I$51,$I$5)</f>
+        <v>3</v>
+      </c>
     </row>
     <row r="16" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B16" s="3" t="s">
@@ -5952,13 +6445,24 @@
       <c r="D16" s="2">
         <v>3</v>
       </c>
+      <c r="G16" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="H16" s="2">
+        <f>COUNTIFS(SPORTSMEN!$K$1:$K$51,ANALYSIS!$G16,SPORTSMEN!$I$1:$I$51,ANALYSIS!$H$5)</f>
+        <v>3</v>
+      </c>
+      <c r="I16" s="2">
+        <f>COUNTIFS(SPORTSMEN!$K$1:$K$51,ANALYSIS!$G16,SPORTSMEN!$I$1:$I$51,$I$5)</f>
+        <v>4</v>
+      </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="G4:G14">
-    <sortCondition ref="G4:G14"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="G6:G16">
+    <sortCondition ref="G6:G16"/>
   </sortState>
   <mergeCells count="1">
-    <mergeCell ref="H2:I2"/>
+    <mergeCell ref="H4:I4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -7317,6 +7821,14 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId2"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{A8765BA9-456A-4dab-B4F3-ACF838C121DE}">
+      <x14:slicerList>
+        <x14:slicer r:id="rId3"/>
+      </x14:slicerList>
+    </ext>
+  </extLst>
 </worksheet>
 </file>
 
